--- a/docagent_clean_mvp/sample_data/raw_excels/SIG_SetB.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/SIG_SetB.xlsx
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A documented Business Continuity Plan is tested via full failover simulation at least once per year.</t>
+          <t>Standard Business Continuity Management control mandates that a documented Business Continuity Plan is tested via full failover simulation at least once per year. [SIG-077]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Compliant - annual failover test passed</t>
+          <t>In progress - remediation scheduled</t>
         </is>
       </c>
     </row>
